--- a/Models/Птицы/results/Птица - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1116.18</v>
+        <v>1549.74</v>
       </c>
       <c r="C2" t="n">
-        <v>968.54</v>
+        <v>1361.35</v>
       </c>
       <c r="D2" t="n">
-        <v>9.27</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.09</v>
+        <v>41.1</v>
       </c>
       <c r="C3" t="n">
-        <v>36.86</v>
+        <v>31.75</v>
       </c>
       <c r="D3" t="n">
-        <v>356.69</v>
+        <v>285.19</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1318.64</v>
+        <v>1434.51</v>
       </c>
       <c r="C4" t="n">
-        <v>1170.44</v>
+        <v>1216.58</v>
       </c>
       <c r="D4" t="n">
-        <v>9.93</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.06</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.03</v>
-      </c>
       <c r="D5" t="n">
-        <v>3.505499728190417e+21</v>
+        <v>6.464043096337895e+18</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>580.97</v>
+        <v>468.7</v>
       </c>
       <c r="C6" t="n">
-        <v>549.8200000000001</v>
+        <v>428.07</v>
       </c>
       <c r="D6" t="n">
-        <v>8.74</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22</v>
+        <v>2.54</v>
       </c>
       <c r="C7" t="n">
-        <v>0.17</v>
+        <v>1.8</v>
       </c>
       <c r="D7" t="n">
-        <v>168.59</v>
+        <v>1801.25</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3.241854430252585e+19</v>
+        <v>1.700944266158386e+20</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.27</v>
+        <v>8.19</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01</v>
+        <v>6.9</v>
       </c>
       <c r="D9" t="n">
-        <v>780.23</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>373.67</v>
+        <v>604.21</v>
       </c>
       <c r="C10" t="n">
-        <v>325.07</v>
+        <v>552.49</v>
       </c>
       <c r="D10" t="n">
-        <v>19.32</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>164.23</v>
+        <v>178.19</v>
       </c>
       <c r="C11" t="n">
-        <v>139.76</v>
+        <v>151.7</v>
       </c>
       <c r="D11" t="n">
-        <v>13.88</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>163.98</v>
+        <v>161.51</v>
       </c>
       <c r="C12" t="n">
-        <v>150.08</v>
+        <v>152.14</v>
       </c>
       <c r="D12" t="n">
-        <v>14.62</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>307.66</v>
+        <v>237.77</v>
       </c>
       <c r="C13" t="n">
-        <v>259.55</v>
+        <v>193.26</v>
       </c>
       <c r="D13" t="n">
-        <v>29.56</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.51</v>
+        <v>7.86</v>
       </c>
       <c r="C14" t="n">
-        <v>6.2</v>
+        <v>5.55</v>
       </c>
       <c r="D14" t="n">
-        <v>74.51000000000001</v>
+        <v>328.85</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2666.19</v>
+        <v>1768.85</v>
       </c>
       <c r="C15" t="n">
-        <v>2559.99</v>
+        <v>1690.17</v>
       </c>
       <c r="D15" t="n">
-        <v>370.55</v>
+        <v>263.68</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>142.36</v>
+        <v>187.11</v>
       </c>
       <c r="C16" t="n">
-        <v>132.94</v>
+        <v>156.44</v>
       </c>
       <c r="D16" t="n">
-        <v>7.11</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>114.46</v>
+        <v>477.64</v>
       </c>
       <c r="C17" t="n">
-        <v>102.51</v>
+        <v>364.69</v>
       </c>
       <c r="D17" t="n">
-        <v>175.35</v>
+        <v>613.87</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0.86</v>
       </c>
       <c r="C18" t="n">
-        <v>2.44</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>1.638749917683986e+23</v>
+        <v>3.073956394307394e+16</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>130.37</v>
+        <v>171.24</v>
       </c>
       <c r="C19" t="n">
-        <v>121.32</v>
+        <v>157.96</v>
       </c>
       <c r="D19" t="n">
-        <v>52.35</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>140.52</v>
+        <v>295.83</v>
       </c>
       <c r="C20" t="n">
-        <v>126.64</v>
+        <v>281.66</v>
       </c>
       <c r="D20" t="n">
-        <v>89.63</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>407.72</v>
+        <v>254.46</v>
       </c>
       <c r="C21" t="n">
-        <v>379.88</v>
+        <v>239.14</v>
       </c>
       <c r="D21" t="n">
-        <v>74.95</v>
+        <v>33.17</v>
       </c>
     </row>
   </sheetData>
